--- a/ImportExample.xlsx
+++ b/ImportExample.xlsx
@@ -5,25 +5,40 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crtct.sharepoint.com/sites/cloud/CRT Cloud Drive/CRT IT Department/Projects/Paycom/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mapheyp\Documents\GitHub\PARS---Standalone-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_9833B7B40F50A426B83EA1EEE757CDE546764D4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F489F99-0D55-42B4-9348-BCACF15EBB1F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7E9B83-8F4F-4C74-A344-8B37F4914D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="58575" yWindow="2625" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="EmployeeInfoE" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Report Data'!$A$1:$AE$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Report Data'!$A$1:$AE$60</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="229">
   <si>
     <t>Employee_Name</t>
   </si>
@@ -680,6 +695,36 @@
   </si>
   <si>
     <t>03/27/2026 16:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee Code </t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Pay Type</t>
+  </si>
+  <si>
+    <t>Total Hours</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>RecordID</t>
+  </si>
+  <si>
+    <t>TimeCardDayID</t>
+  </si>
+  <si>
+    <t>TimeCardID</t>
   </si>
 </sst>
 </file>
@@ -1041,9 +1086,35 @@
   <dimension ref="A1:AE60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="22.42578125" customWidth="1"/>
-    <col min="13" max="13" width="28.42578125" customWidth="1"/>
+    <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -5869,12 +5940,1290 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:AE57" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AE60" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FFA9AA1-9FD9-4741-947B-5EDC278026BA}">
+  <dimension ref="A1:AC15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="1">
+        <v>8.25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2">
+        <v>19979</v>
+      </c>
+      <c r="U2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2">
+        <v>900</v>
+      </c>
+      <c r="W2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2">
+        <v>699</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2">
+        <v>23</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB2">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="1">
+        <v>8.25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3">
+        <v>19979</v>
+      </c>
+      <c r="U3" t="s">
+        <v>32</v>
+      </c>
+      <c r="V3">
+        <v>900</v>
+      </c>
+      <c r="W3" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3">
+        <v>699</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3">
+        <v>23</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1">
+        <v>8.25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T4">
+        <v>19979</v>
+      </c>
+      <c r="U4" t="s">
+        <v>32</v>
+      </c>
+      <c r="V4">
+        <v>900</v>
+      </c>
+      <c r="W4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4">
+        <v>699</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4">
+        <v>23</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB4">
+        <v>2</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" t="s">
+        <v>54</v>
+      </c>
+      <c r="S5" t="s">
+        <v>30</v>
+      </c>
+      <c r="T5">
+        <v>19979</v>
+      </c>
+      <c r="U5" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5">
+        <v>900</v>
+      </c>
+      <c r="W5" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5">
+        <v>699</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z5">
+        <v>23</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB5">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1">
+        <v>6.75</v>
+      </c>
+      <c r="I6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>30</v>
+      </c>
+      <c r="T6">
+        <v>19979</v>
+      </c>
+      <c r="U6" t="s">
+        <v>32</v>
+      </c>
+      <c r="V6">
+        <v>900</v>
+      </c>
+      <c r="W6" t="s">
+        <v>40</v>
+      </c>
+      <c r="X6">
+        <v>699</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z6">
+        <v>23</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB6">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" t="s">
+        <v>60</v>
+      </c>
+      <c r="N7" t="s">
+        <v>57</v>
+      </c>
+      <c r="O7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>30</v>
+      </c>
+      <c r="T7">
+        <v>19979</v>
+      </c>
+      <c r="U7" t="s">
+        <v>32</v>
+      </c>
+      <c r="V7">
+        <v>900</v>
+      </c>
+      <c r="W7" t="s">
+        <v>40</v>
+      </c>
+      <c r="X7">
+        <v>699</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z7">
+        <v>23</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB7">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" t="s">
+        <v>64</v>
+      </c>
+      <c r="S8" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8">
+        <v>19979</v>
+      </c>
+      <c r="U8" t="s">
+        <v>32</v>
+      </c>
+      <c r="V8">
+        <v>900</v>
+      </c>
+      <c r="W8" t="s">
+        <v>40</v>
+      </c>
+      <c r="X8">
+        <v>699</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z8">
+        <v>23</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB8">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="1">
+        <v>7.25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" t="s">
+        <v>66</v>
+      </c>
+      <c r="O9" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T9">
+        <v>19979</v>
+      </c>
+      <c r="U9" t="s">
+        <v>32</v>
+      </c>
+      <c r="V9">
+        <v>900</v>
+      </c>
+      <c r="W9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X9">
+        <v>699</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z9">
+        <v>23</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB9">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" t="s">
+        <v>70</v>
+      </c>
+      <c r="S10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10">
+        <v>19979</v>
+      </c>
+      <c r="U10" t="s">
+        <v>32</v>
+      </c>
+      <c r="V10">
+        <v>900</v>
+      </c>
+      <c r="W10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X10">
+        <v>699</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z10">
+        <v>23</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB10">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="I11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" t="s">
+        <v>73</v>
+      </c>
+      <c r="S11" t="s">
+        <v>30</v>
+      </c>
+      <c r="T11">
+        <v>19979</v>
+      </c>
+      <c r="U11" t="s">
+        <v>32</v>
+      </c>
+      <c r="V11">
+        <v>900</v>
+      </c>
+      <c r="W11" t="s">
+        <v>40</v>
+      </c>
+      <c r="X11">
+        <v>699</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z11">
+        <v>23</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB11">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" t="s">
+        <v>75</v>
+      </c>
+      <c r="M12" t="s">
+        <v>36</v>
+      </c>
+      <c r="N12" t="s">
+        <v>76</v>
+      </c>
+      <c r="O12" t="s">
+        <v>77</v>
+      </c>
+      <c r="S12" t="s">
+        <v>30</v>
+      </c>
+      <c r="T12">
+        <v>19979</v>
+      </c>
+      <c r="U12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V12">
+        <v>900</v>
+      </c>
+      <c r="W12" t="s">
+        <v>40</v>
+      </c>
+      <c r="X12">
+        <v>699</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z12">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB12">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="1">
+        <v>8.25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" t="s">
+        <v>79</v>
+      </c>
+      <c r="M13" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" t="s">
+        <v>80</v>
+      </c>
+      <c r="O13" t="s">
+        <v>81</v>
+      </c>
+      <c r="S13" t="s">
+        <v>30</v>
+      </c>
+      <c r="T13">
+        <v>19979</v>
+      </c>
+      <c r="U13" t="s">
+        <v>32</v>
+      </c>
+      <c r="V13">
+        <v>900</v>
+      </c>
+      <c r="W13" t="s">
+        <v>40</v>
+      </c>
+      <c r="X13">
+        <v>699</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z13">
+        <v>23</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB13">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="1">
+        <v>8.25</v>
+      </c>
+      <c r="I14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" t="s">
+        <v>82</v>
+      </c>
+      <c r="K14" t="s">
+        <v>83</v>
+      </c>
+      <c r="M14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" t="s">
+        <v>214</v>
+      </c>
+      <c r="O14" t="s">
+        <v>197</v>
+      </c>
+      <c r="S14" t="s">
+        <v>30</v>
+      </c>
+      <c r="T14">
+        <v>19979</v>
+      </c>
+      <c r="U14" t="s">
+        <v>32</v>
+      </c>
+      <c r="V14">
+        <v>900</v>
+      </c>
+      <c r="W14" t="s">
+        <v>40</v>
+      </c>
+      <c r="X14">
+        <v>699</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z14">
+        <v>23</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB14">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="1">
+        <v>8.25</v>
+      </c>
+      <c r="I15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" t="s">
+        <v>215</v>
+      </c>
+      <c r="K15" t="s">
+        <v>216</v>
+      </c>
+      <c r="M15" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" t="s">
+        <v>217</v>
+      </c>
+      <c r="O15" t="s">
+        <v>218</v>
+      </c>
+      <c r="S15" t="s">
+        <v>30</v>
+      </c>
+      <c r="T15">
+        <v>19979</v>
+      </c>
+      <c r="U15" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15">
+        <v>900</v>
+      </c>
+      <c r="W15" t="s">
+        <v>40</v>
+      </c>
+      <c r="X15">
+        <v>699</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z15">
+        <v>23</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB15">
+        <v>2</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18B0C0D4-1287-4C2B-A1CC-8AE6C7E13B08}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ListType xmlns="dfa1a86b-2561-42b1-b282-d176b9ac45bc" xsi:nil="true"/>
+    <TaxCatchAll xmlns="b1200c16-19fc-4b91-838f-670ae6f905df" xsi:nil="true"/>
+    <InvoiceStatus xmlns="dfa1a86b-2561-42b1-b282-d176b9ac45bc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dfa1a86b-2561-42b1-b282-d176b9ac45bc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Status xmlns="dfa1a86b-2561-42b1-b282-d176b9ac45bc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B54286F5E2CCD94887844FE3E8ECADBD" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ad8fcee36e600513822ed67adb99b979">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b1200c16-19fc-4b91-838f-670ae6f905df" xmlns:ns3="dfa1a86b-2561-42b1-b282-d176b9ac45bc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3889fb0b1a81e7433a1081ff161c3940" ns2:_="" ns3:_="">
     <xsd:import namespace="b1200c16-19fc-4b91-838f-670ae6f905df"/>
@@ -6144,20 +7493,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ListType xmlns="dfa1a86b-2561-42b1-b282-d176b9ac45bc" xsi:nil="true"/>
-    <TaxCatchAll xmlns="b1200c16-19fc-4b91-838f-670ae6f905df" xsi:nil="true"/>
-    <InvoiceStatus xmlns="dfa1a86b-2561-42b1-b282-d176b9ac45bc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dfa1a86b-2561-42b1-b282-d176b9ac45bc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Status xmlns="dfa1a86b-2561-42b1-b282-d176b9ac45bc" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6168,6 +7503,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03D498A9-1060-4C2B-A7C2-84C460899AD9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dfa1a86b-2561-42b1-b282-d176b9ac45bc"/>
+    <ds:schemaRef ds:uri="b1200c16-19fc-4b91-838f-670ae6f905df"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE5CF02A-D26A-4E03-B015-6D8A7F3F558B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6186,17 +7532,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03D498A9-1060-4C2B-A7C2-84C460899AD9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dfa1a86b-2561-42b1-b282-d176b9ac45bc"/>
-    <ds:schemaRef ds:uri="b1200c16-19fc-4b91-838f-670ae6f905df"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D285058-7C70-4E0C-B802-744017302029}">
   <ds:schemaRefs>
